--- a/Ex_Import/Schedule_Import.xlsx
+++ b/Ex_Import/Schedule_Import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\SchoolBellSystem\Ex_Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D9768E-2B9E-4FD4-9F3A-A414E935A71F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADC1C08-06B5-4087-BCCF-130F0A7C47E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{101D1E43-D536-4C52-9D44-9208FA8FD114}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="67">
   <si>
     <t>שעת התחלה</t>
   </si>
@@ -60,12 +60,6 @@
     <t>שעת 0</t>
   </si>
   <si>
-    <t>Tune 4.mp3</t>
-  </si>
-  <si>
-    <t>D:\Projects\SchoolBellSystem\audio\Tune 4.mp3</t>
-  </si>
-  <si>
     <t>Text</t>
   </si>
   <si>
@@ -114,9 +108,6 @@
     <t>09:40:00</t>
   </si>
   <si>
-    <t>Ring 1.mp3</t>
-  </si>
-  <si>
     <t>תרגיל - כניסה למרחב מוגן</t>
   </si>
   <si>
@@ -138,9 +129,6 @@
     <t>10:25:31</t>
   </si>
   <si>
-    <t>(♫)D:\...\סליחות</t>
-  </si>
-  <si>
     <t>10:43:00</t>
   </si>
   <si>
@@ -244,6 +232,12 @@
   </si>
   <si>
     <t>music</t>
+  </si>
+  <si>
+    <t>bell_standard.mp3</t>
+  </si>
+  <si>
+    <t>song_1.mp3</t>
   </si>
 </sst>
 </file>
@@ -253,10 +247,17 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="177"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
@@ -663,7 +664,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -705,54 +706,54 @@
         <v>7</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" t="s">
         <v>58</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="M2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" t="s">
+        <v>61</v>
+      </c>
+      <c r="O2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" t="s">
-        <v>62</v>
-      </c>
-      <c r="M2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" t="s">
-        <v>65</v>
-      </c>
-      <c r="O2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -766,10 +767,10 @@
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>85</v>
@@ -801,19 +802,19 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>85</v>
@@ -845,19 +846,19 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4">
         <v>10</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>7</v>
+      <c r="E5" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -889,19 +890,19 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1">
         <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>85</v>
@@ -933,19 +934,19 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7">
         <v>70</v>
@@ -977,63 +978,63 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4">
         <v>30</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>85</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1">
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G9">
         <v>90</v>
@@ -1065,19 +1066,19 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="4">
         <v>1049</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>85</v>
@@ -1109,19 +1110,19 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>70</v>
@@ -1153,19 +1154,19 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4">
         <v>30</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>25</v>
+      <c r="E12" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>85</v>
@@ -1197,19 +1198,19 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D13" s="1">
         <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>85</v>
@@ -1241,19 +1242,19 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" s="4">
         <v>30</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>25</v>
+      <c r="E14" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>85</v>
@@ -1285,19 +1286,19 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4">
         <v>749</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>70</v>
@@ -1329,19 +1330,19 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1">
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16">
         <v>90</v>
@@ -1373,19 +1374,19 @@
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D17" s="4">
         <v>30</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>25</v>
+      <c r="E17" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17">
         <v>85</v>
@@ -1417,19 +1418,19 @@
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1">
         <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>85</v>
@@ -1461,19 +1462,19 @@
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D19" s="1">
         <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19">
         <v>85</v>
@@ -1505,19 +1506,19 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D20" s="4">
         <v>30</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>7</v>
+      <c r="E20" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>60</v>
@@ -1549,19 +1550,19 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D21" s="1">
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G21">
         <v>85</v>
@@ -1593,19 +1594,19 @@
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D22" s="4">
         <v>30</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>7</v>
+      <c r="E22" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G22">
         <v>85</v>
@@ -1637,19 +1638,19 @@
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D23" s="4">
         <v>15</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>7</v>
+      <c r="E23" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>85</v>
@@ -1681,19 +1682,19 @@
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1">
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>60</v>
@@ -1725,19 +1726,19 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D25" s="4">
         <v>30</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>7</v>
+      <c r="E25" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G25">
         <v>85</v>
@@ -1768,6 +1769,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>